--- a/budget-2027/dist/Planner-2027-EN.xlsx
+++ b/budget-2027/dist/Planner-2027-EN.xlsx
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="136">
   <si>
     <t xml:space="preserve">2027 Budget, Goals &amp; Ramadan Planner</t>
   </si>
@@ -432,6 +432,9 @@
     <t xml:space="preserve">Charity</t>
   </si>
   <si>
+    <t xml:space="preserve">✓</t>
+  </si>
+  <si>
     <t xml:space="preserve">Days until Ramadan</t>
   </si>
   <si>
@@ -442,6 +445,9 @@
   </si>
   <si>
     <t xml:space="preserve">Actual in Ramadan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">✗</t>
   </si>
   <si>
     <t xml:space="preserve">All expenses during Ramadan</t>
@@ -1366,11 +1372,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="39420429"/>
-        <c:axId val="99753091"/>
+        <c:axId val="76799047"/>
+        <c:axId val="14437553"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="39420429"/>
+        <c:axId val="76799047"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1402,7 +1408,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="99753091"/>
+        <c:crossAx val="14437553"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1410,7 +1416,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="99753091"/>
+        <c:axId val="14437553"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1452,7 +1458,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="39420429"/>
+        <c:crossAx val="76799047"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1768,11 +1774,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="22669065"/>
-        <c:axId val="95950224"/>
+        <c:axId val="62317453"/>
+        <c:axId val="74808980"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="22669065"/>
+        <c:axId val="62317453"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -1804,7 +1810,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="95950224"/>
+        <c:crossAx val="74808980"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1812,7 +1818,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="95950224"/>
+        <c:axId val="74808980"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1854,7 +1860,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="22669065"/>
+        <c:crossAx val="62317453"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2247,11 +2253,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="25127875"/>
-        <c:axId val="54329792"/>
+        <c:axId val="88926621"/>
+        <c:axId val="74603430"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="25127875"/>
+        <c:axId val="88926621"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2283,7 +2289,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="54329792"/>
+        <c:crossAx val="74603430"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2291,7 +2297,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="54329792"/>
+        <c:axId val="74603430"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2333,7 +2339,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="25127875"/>
+        <c:crossAx val="88926621"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2395,8 +2401,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>259920</xdr:colOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>511560</xdr:colOff>
       <xdr:row>25</xdr:row>
       <xdr:rowOff>1080</xdr:rowOff>
     </xdr:to>
@@ -2407,7 +2413,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="7471440" y="2238480"/>
-        <a:ext cx="5759640" cy="3239640"/>
+        <a:ext cx="5399640" cy="3239640"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2425,10 +2431,10 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>262080</xdr:colOff>
-      <xdr:row>55</xdr:row>
-      <xdr:rowOff>44640</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>785520</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>149760</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2437,7 +2443,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="141120" y="5477040"/>
-        <a:ext cx="5759640" cy="5759640"/>
+        <a:ext cx="7199640" cy="3959640"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -21978,7 +21984,7 @@
         <v>40500</v>
       </c>
       <c r="H6" s="28" t="n">
-        <f aca="false">IF(E6=0,0,F6/E6)</f>
+        <f aca="false">IF(OR(B6="",E6=0),"",F6/E6)</f>
         <v>0.25</v>
       </c>
     </row>
@@ -22005,7 +22011,7 @@
         <v>10339</v>
       </c>
       <c r="H7" s="28" t="n">
-        <f aca="false">IF(E7=0,0,F7/E7)</f>
+        <f aca="false">IF(OR(B7="",E7=0),"",F7/E7)</f>
         <v>0.282013888888889</v>
       </c>
     </row>
@@ -22032,7 +22038,7 @@
         <v>2536</v>
       </c>
       <c r="H8" s="28" t="n">
-        <f aca="false">IF(E8=0,0,F8/E8)</f>
+        <f aca="false">IF(OR(B8="",E8=0),"",F8/E8)</f>
         <v>0.154666666666667</v>
       </c>
     </row>
@@ -22054,9 +22060,9 @@
         <f aca="false">E9-F9</f>
         <v>0</v>
       </c>
-      <c r="H9" s="28" t="n">
-        <f aca="false">IF(E9=0,0,F9/E9)</f>
-        <v>0</v>
+      <c r="H9" s="28" t="str">
+        <f aca="false">IF(OR(B9="",E9=0),"",F9/E9)</f>
+        <v/>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22077,9 +22083,9 @@
         <f aca="false">E10-F10</f>
         <v>0</v>
       </c>
-      <c r="H10" s="28" t="n">
-        <f aca="false">IF(E10=0,0,F10/E10)</f>
-        <v>0</v>
+      <c r="H10" s="28" t="str">
+        <f aca="false">IF(OR(B10="",E10=0),"",F10/E10)</f>
+        <v/>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22100,9 +22106,9 @@
         <f aca="false">E11-F11</f>
         <v>0</v>
       </c>
-      <c r="H11" s="28" t="n">
-        <f aca="false">IF(E11=0,0,F11/E11)</f>
-        <v>0</v>
+      <c r="H11" s="28" t="str">
+        <f aca="false">IF(OR(B11="",E11=0),"",F11/E11)</f>
+        <v/>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22123,9 +22129,9 @@
         <f aca="false">E12-F12</f>
         <v>0</v>
       </c>
-      <c r="H12" s="28" t="n">
-        <f aca="false">IF(E12=0,0,F12/E12)</f>
-        <v>0</v>
+      <c r="H12" s="28" t="str">
+        <f aca="false">IF(OR(B12="",E12=0),"",F12/E12)</f>
+        <v/>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22146,9 +22152,9 @@
         <f aca="false">E13-F13</f>
         <v>0</v>
       </c>
-      <c r="H13" s="28" t="n">
-        <f aca="false">IF(E13=0,0,F13/E13)</f>
-        <v>0</v>
+      <c r="H13" s="28" t="str">
+        <f aca="false">IF(OR(B13="",E13=0),"",F13/E13)</f>
+        <v/>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22174,7 +22180,7 @@
         <v>12600</v>
       </c>
       <c r="H14" s="28" t="n">
-        <f aca="false">IF(E14=0,0,F14/E14)</f>
+        <f aca="false">IF(OR(B14="",E14=0),"",F14/E14)</f>
         <v>0.25</v>
       </c>
     </row>
@@ -22201,7 +22207,7 @@
         <v>2285</v>
       </c>
       <c r="H15" s="28" t="n">
-        <f aca="false">IF(E15=0,0,F15/E15)</f>
+        <f aca="false">IF(OR(B15="",E15=0),"",F15/E15)</f>
         <v>0.238333333333333</v>
       </c>
     </row>
@@ -22228,7 +22234,7 @@
         <v>5342</v>
       </c>
       <c r="H16" s="28" t="n">
-        <f aca="false">IF(E16=0,0,F16/E16)</f>
+        <f aca="false">IF(OR(B16="",E16=0),"",F16/E16)</f>
         <v>0.258055555555556</v>
       </c>
     </row>
@@ -22255,7 +22261,7 @@
         <v>2273</v>
       </c>
       <c r="H17" s="28" t="n">
-        <f aca="false">IF(E17=0,0,F17/E17)</f>
+        <f aca="false">IF(OR(B17="",E17=0),"",F17/E17)</f>
         <v>0.242333333333333</v>
       </c>
     </row>
@@ -22282,7 +22288,7 @@
         <v>720</v>
       </c>
       <c r="H18" s="28" t="n">
-        <f aca="false">IF(E18=0,0,F18/E18)</f>
+        <f aca="false">IF(OR(B18="",E18=0),"",F18/E18)</f>
         <v>0.25</v>
       </c>
     </row>
@@ -22309,7 +22315,7 @@
         <v>1272</v>
       </c>
       <c r="H19" s="28" t="n">
-        <f aca="false">IF(E19=0,0,F19/E19)</f>
+        <f aca="false">IF(OR(B19="",E19=0),"",F19/E19)</f>
         <v>0.116666666666667</v>
       </c>
     </row>
@@ -22336,7 +22342,7 @@
         <v>1500</v>
       </c>
       <c r="H20" s="28" t="n">
-        <f aca="false">IF(E20=0,0,F20/E20)</f>
+        <f aca="false">IF(OR(B20="",E20=0),"",F20/E20)</f>
         <v>0.166666666666667</v>
       </c>
     </row>
@@ -22363,7 +22369,7 @@
         <v>1831</v>
       </c>
       <c r="H21" s="28" t="n">
-        <f aca="false">IF(E21=0,0,F21/E21)</f>
+        <f aca="false">IF(OR(B21="",E21=0),"",F21/E21)</f>
         <v>0.237083333333333</v>
       </c>
     </row>
@@ -22390,7 +22396,7 @@
         <v>1260</v>
       </c>
       <c r="H22" s="28" t="n">
-        <f aca="false">IF(E22=0,0,F22/E22)</f>
+        <f aca="false">IF(OR(B22="",E22=0),"",F22/E22)</f>
         <v>0.125</v>
       </c>
     </row>
@@ -22417,7 +22423,7 @@
         <v>540</v>
       </c>
       <c r="H23" s="28" t="n">
-        <f aca="false">IF(E23=0,0,F23/E23)</f>
+        <f aca="false">IF(OR(B23="",E23=0),"",F23/E23)</f>
         <v>0.25</v>
       </c>
     </row>
@@ -22444,7 +22450,7 @@
         <v>1341</v>
       </c>
       <c r="H24" s="28" t="n">
-        <f aca="false">IF(E24=0,0,F24/E24)</f>
+        <f aca="false">IF(OR(B24="",E24=0),"",F24/E24)</f>
         <v>0.255</v>
       </c>
     </row>
@@ -22470,9 +22476,9 @@
         <f aca="false">E25-F25</f>
         <v>-684</v>
       </c>
-      <c r="H25" s="28" t="n">
-        <f aca="false">IF(E25=0,0,F25/E25)</f>
-        <v>0</v>
+      <c r="H25" s="28" t="str">
+        <f aca="false">IF(OR(B25="",E25=0),"",F25/E25)</f>
+        <v/>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22497,9 +22503,9 @@
         <f aca="false">E26-F26</f>
         <v>-696</v>
       </c>
-      <c r="H26" s="28" t="n">
-        <f aca="false">IF(E26=0,0,F26/E26)</f>
-        <v>0</v>
+      <c r="H26" s="28" t="str">
+        <f aca="false">IF(OR(B26="",E26=0),"",F26/E26)</f>
+        <v/>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22524,9 +22530,9 @@
         <f aca="false">E27-F27</f>
         <v>-312</v>
       </c>
-      <c r="H27" s="28" t="n">
-        <f aca="false">IF(E27=0,0,F27/E27)</f>
-        <v>0</v>
+      <c r="H27" s="28" t="str">
+        <f aca="false">IF(OR(B27="",E27=0),"",F27/E27)</f>
+        <v/>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22551,9 +22557,9 @@
         <f aca="false">E28-F28</f>
         <v>-348</v>
       </c>
-      <c r="H28" s="28" t="n">
-        <f aca="false">IF(E28=0,0,F28/E28)</f>
-        <v>0</v>
+      <c r="H28" s="28" t="str">
+        <f aca="false">IF(OR(B28="",E28=0),"",F28/E28)</f>
+        <v/>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22574,9 +22580,9 @@
         <f aca="false">E29-F29</f>
         <v>0</v>
       </c>
-      <c r="H29" s="28" t="n">
-        <f aca="false">IF(E29=0,0,F29/E29)</f>
-        <v>0</v>
+      <c r="H29" s="28" t="str">
+        <f aca="false">IF(OR(B29="",E29=0),"",F29/E29)</f>
+        <v/>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22597,9 +22603,9 @@
         <f aca="false">E30-F30</f>
         <v>0</v>
       </c>
-      <c r="H30" s="28" t="n">
-        <f aca="false">IF(E30=0,0,F30/E30)</f>
-        <v>0</v>
+      <c r="H30" s="28" t="str">
+        <f aca="false">IF(OR(B30="",E30=0),"",F30/E30)</f>
+        <v/>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22620,9 +22626,9 @@
         <f aca="false">E31-F31</f>
         <v>0</v>
       </c>
-      <c r="H31" s="28" t="n">
-        <f aca="false">IF(E31=0,0,F31/E31)</f>
-        <v>0</v>
+      <c r="H31" s="28" t="str">
+        <f aca="false">IF(OR(B31="",E31=0),"",F31/E31)</f>
+        <v/>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22643,9 +22649,9 @@
         <f aca="false">E32-F32</f>
         <v>0</v>
       </c>
-      <c r="H32" s="28" t="n">
-        <f aca="false">IF(E32=0,0,F32/E32)</f>
-        <v>0</v>
+      <c r="H32" s="28" t="str">
+        <f aca="false">IF(OR(B32="",E32=0),"",F32/E32)</f>
+        <v/>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22666,9 +22672,9 @@
         <f aca="false">E33-F33</f>
         <v>0</v>
       </c>
-      <c r="H33" s="28" t="n">
-        <f aca="false">IF(E33=0,0,F33/E33)</f>
-        <v>0</v>
+      <c r="H33" s="28" t="str">
+        <f aca="false">IF(OR(B33="",E33=0),"",F33/E33)</f>
+        <v/>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22689,9 +22695,9 @@
         <f aca="false">E34-F34</f>
         <v>0</v>
       </c>
-      <c r="H34" s="28" t="n">
-        <f aca="false">IF(E34=0,0,F34/E34)</f>
-        <v>0</v>
+      <c r="H34" s="28" t="str">
+        <f aca="false">IF(OR(B34="",E34=0),"",F34/E34)</f>
+        <v/>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22712,9 +22718,9 @@
         <f aca="false">E35-F35</f>
         <v>0</v>
       </c>
-      <c r="H35" s="28" t="n">
-        <f aca="false">IF(E35=0,0,F35/E35)</f>
-        <v>0</v>
+      <c r="H35" s="28" t="str">
+        <f aca="false">IF(OR(B35="",E35=0),"",F35/E35)</f>
+        <v/>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22735,9 +22741,9 @@
         <f aca="false">E36-F36</f>
         <v>0</v>
       </c>
-      <c r="H36" s="28" t="n">
-        <f aca="false">IF(E36=0,0,F36/E36)</f>
-        <v>0</v>
+      <c r="H36" s="28" t="str">
+        <f aca="false">IF(OR(B36="",E36=0),"",F36/E36)</f>
+        <v/>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22758,9 +22764,9 @@
         <f aca="false">E37-F37</f>
         <v>0</v>
       </c>
-      <c r="H37" s="28" t="n">
-        <f aca="false">IF(E37=0,0,F37/E37)</f>
-        <v>0</v>
+      <c r="H37" s="28" t="str">
+        <f aca="false">IF(OR(B37="",E37=0),"",F37/E37)</f>
+        <v/>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22781,9 +22787,9 @@
         <f aca="false">E38-F38</f>
         <v>0</v>
       </c>
-      <c r="H38" s="28" t="n">
-        <f aca="false">IF(E38=0,0,F38/E38)</f>
-        <v>0</v>
+      <c r="H38" s="28" t="str">
+        <f aca="false">IF(OR(B38="",E38=0),"",F38/E38)</f>
+        <v/>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22804,9 +22810,9 @@
         <f aca="false">E39-F39</f>
         <v>0</v>
       </c>
-      <c r="H39" s="28" t="n">
-        <f aca="false">IF(E39=0,0,F39/E39)</f>
-        <v>0</v>
+      <c r="H39" s="28" t="str">
+        <f aca="false">IF(OR(B39="",E39=0),"",F39/E39)</f>
+        <v/>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22827,9 +22833,9 @@
         <f aca="false">E40-F40</f>
         <v>0</v>
       </c>
-      <c r="H40" s="28" t="n">
-        <f aca="false">IF(E40=0,0,F40/E40)</f>
-        <v>0</v>
+      <c r="H40" s="28" t="str">
+        <f aca="false">IF(OR(B40="",E40=0),"",F40/E40)</f>
+        <v/>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22906,7 +22912,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{77A15BDE-7F1B-43E8-986B-451C501F4AB6}</x14:id>
+          <x14:id>{2D50E0D9-5673-428C-8EE0-253E381D341A}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22923,7 +22929,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{77A15BDE-7F1B-43E8-986B-451C501F4AB6}">
+          <x14:cfRule type="dataBar" id="{2D50E0D9-5673-428C-8EE0-253E381D341A}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -23334,7 +23340,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9D1D8D86-BA8C-4BB8-B012-BC4EF3D4AF54}</x14:id>
+          <x14:id>{FBF5F937-FCE5-4328-B969-97B3894B4A9C}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23364,7 +23370,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9D1D8D86-BA8C-4BB8-B012-BC4EF3D4AF54}">
+          <x14:cfRule type="dataBar" id="{FBF5F937-FCE5-4328-B969-97B3894B4A9C}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -23424,7 +23430,7 @@
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
     </row>
-    <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="4" t="s">
         <v>111</v>
       </c>
@@ -23481,14 +23487,22 @@
         <f aca="false">IF(1&gt;cfgRDays,"",cfgRStart+1-1)</f>
         <v>46426</v>
       </c>
-      <c r="J7" s="7"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="12"/>
+      <c r="J7" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="K7" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="M7" s="12" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="32" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C8" s="34" t="n">
         <f aca="true">MAX(0,cfgRStart-TODAY())</f>
@@ -23502,10 +23516,18 @@
         <f aca="false">IF(2&gt;cfgRDays,"",cfgRStart+2-1)</f>
         <v>46427</v>
       </c>
-      <c r="J8" s="7"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="12"/>
+      <c r="J8" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="K8" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="M8" s="12" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H9" s="26" t="n">
@@ -23516,14 +23538,22 @@
         <f aca="false">IF(3&gt;cfgRDays,"",cfgRStart+3-1)</f>
         <v>46428</v>
       </c>
-      <c r="J9" s="7"/>
-      <c r="K9" s="6"/>
-      <c r="L9" s="7"/>
-      <c r="M9" s="12"/>
-    </row>
-    <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="J9" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="K9" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="M9" s="12" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="35" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C10" s="35"/>
       <c r="D10" s="35"/>
@@ -23537,20 +23567,28 @@
         <f aca="false">IF(4&gt;cfgRDays,"",cfgRStart+4-1)</f>
         <v>46429</v>
       </c>
-      <c r="J10" s="7"/>
-      <c r="K10" s="6"/>
-      <c r="L10" s="7"/>
-      <c r="M10" s="12"/>
-    </row>
-    <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="J10" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="K10" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="L10" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="M10" s="12" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="4" t="s">
         <v>49</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>94</v>
@@ -23566,10 +23604,18 @@
         <f aca="false">IF(5&gt;cfgRDays,"",cfgRStart+5-1)</f>
         <v>46430</v>
       </c>
-      <c r="J11" s="7"/>
-      <c r="K11" s="6"/>
-      <c r="L11" s="7"/>
-      <c r="M11" s="12"/>
+      <c r="J11" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="K11" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="L11" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="M11" s="12" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="24" t="s">
@@ -23587,7 +23633,7 @@
         <v>-84</v>
       </c>
       <c r="F12" s="28" t="n">
-        <f aca="false">IF(N(C12)=0,0,D12/C12)</f>
+        <f aca="false">IF(N(C12)=0,"",D12/C12)</f>
         <v>1.14</v>
       </c>
       <c r="H12" s="26" t="n">
@@ -23598,10 +23644,18 @@
         <f aca="false">IF(6&gt;cfgRDays,"",cfgRStart+6-1)</f>
         <v>46431</v>
       </c>
-      <c r="J12" s="7"/>
-      <c r="K12" s="6"/>
-      <c r="L12" s="7"/>
-      <c r="M12" s="12"/>
+      <c r="J12" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="K12" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="L12" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="M12" s="12" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="24" t="s">
@@ -23619,7 +23673,7 @@
         <v>4</v>
       </c>
       <c r="F13" s="28" t="n">
-        <f aca="false">IF(N(C13)=0,0,D13/C13)</f>
+        <f aca="false">IF(N(C13)=0,"",D13/C13)</f>
         <v>0.994285714285714</v>
       </c>
       <c r="H13" s="26" t="n">
@@ -23630,10 +23684,18 @@
         <f aca="false">IF(7&gt;cfgRDays,"",cfgRStart+7-1)</f>
         <v>46432</v>
       </c>
-      <c r="J13" s="7"/>
-      <c r="K13" s="6"/>
-      <c r="L13" s="7"/>
-      <c r="M13" s="12"/>
+      <c r="J13" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="K13" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="L13" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="M13" s="12" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="24" t="s">
@@ -23651,7 +23713,7 @@
         <v>-12</v>
       </c>
       <c r="F14" s="28" t="n">
-        <f aca="false">IF(N(C14)=0,0,D14/C14)</f>
+        <f aca="false">IF(N(C14)=0,"",D14/C14)</f>
         <v>1.04</v>
       </c>
       <c r="H14" s="26" t="n">
@@ -23662,10 +23724,18 @@
         <f aca="false">IF(8&gt;cfgRDays,"",cfgRStart+8-1)</f>
         <v>46433</v>
       </c>
-      <c r="J14" s="7"/>
-      <c r="K14" s="6"/>
-      <c r="L14" s="7"/>
-      <c r="M14" s="12"/>
+      <c r="J14" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="K14" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="L14" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="M14" s="12" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="24" t="s">
@@ -23683,7 +23753,7 @@
         <v>-98</v>
       </c>
       <c r="F15" s="28" t="n">
-        <f aca="false">IF(N(C15)=0,0,D15/C15)</f>
+        <f aca="false">IF(N(C15)=0,"",D15/C15)</f>
         <v>1.392</v>
       </c>
       <c r="H15" s="26" t="n">
@@ -23694,10 +23764,18 @@
         <f aca="false">IF(9&gt;cfgRDays,"",cfgRStart+9-1)</f>
         <v>46434</v>
       </c>
-      <c r="J15" s="7"/>
-      <c r="K15" s="6"/>
-      <c r="L15" s="7"/>
-      <c r="M15" s="12"/>
+      <c r="J15" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="K15" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="L15" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="M15" s="12" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="24"/>
@@ -23710,9 +23788,9 @@
         <f aca="false">N(C16)-D16</f>
         <v>0</v>
       </c>
-      <c r="F16" s="28" t="n">
-        <f aca="false">IF(N(C16)=0,0,D16/C16)</f>
-        <v>0</v>
+      <c r="F16" s="28" t="str">
+        <f aca="false">IF(N(C16)=0,"",D16/C16)</f>
+        <v/>
       </c>
       <c r="H16" s="26" t="n">
         <f aca="false">IF(10&gt;cfgRDays,"",10)</f>
@@ -23722,10 +23800,18 @@
         <f aca="false">IF(10&gt;cfgRDays,"",cfgRStart+10-1)</f>
         <v>46435</v>
       </c>
-      <c r="J16" s="7"/>
-      <c r="K16" s="6"/>
-      <c r="L16" s="7"/>
-      <c r="M16" s="12"/>
+      <c r="J16" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="K16" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="L16" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="M16" s="12" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="24"/>
@@ -23738,9 +23824,9 @@
         <f aca="false">N(C17)-D17</f>
         <v>0</v>
       </c>
-      <c r="F17" s="28" t="n">
-        <f aca="false">IF(N(C17)=0,0,D17/C17)</f>
-        <v>0</v>
+      <c r="F17" s="28" t="str">
+        <f aca="false">IF(N(C17)=0,"",D17/C17)</f>
+        <v/>
       </c>
       <c r="H17" s="26" t="n">
         <f aca="false">IF(11&gt;cfgRDays,"",11)</f>
@@ -23750,10 +23836,18 @@
         <f aca="false">IF(11&gt;cfgRDays,"",cfgRStart+11-1)</f>
         <v>46436</v>
       </c>
-      <c r="J17" s="7"/>
-      <c r="K17" s="6"/>
-      <c r="L17" s="7"/>
-      <c r="M17" s="12"/>
+      <c r="J17" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="K17" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="L17" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="M17" s="12" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="24"/>
@@ -23766,9 +23860,9 @@
         <f aca="false">N(C18)-D18</f>
         <v>0</v>
       </c>
-      <c r="F18" s="28" t="n">
-        <f aca="false">IF(N(C18)=0,0,D18/C18)</f>
-        <v>0</v>
+      <c r="F18" s="28" t="str">
+        <f aca="false">IF(N(C18)=0,"",D18/C18)</f>
+        <v/>
       </c>
       <c r="H18" s="26" t="n">
         <f aca="false">IF(12&gt;cfgRDays,"",12)</f>
@@ -23778,10 +23872,18 @@
         <f aca="false">IF(12&gt;cfgRDays,"",cfgRStart+12-1)</f>
         <v>46437</v>
       </c>
-      <c r="J18" s="7"/>
-      <c r="K18" s="6"/>
-      <c r="L18" s="7"/>
-      <c r="M18" s="12"/>
+      <c r="J18" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="K18" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="L18" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="M18" s="12" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="24"/>
@@ -23794,9 +23896,9 @@
         <f aca="false">N(C19)-D19</f>
         <v>0</v>
       </c>
-      <c r="F19" s="28" t="n">
-        <f aca="false">IF(N(C19)=0,0,D19/C19)</f>
-        <v>0</v>
+      <c r="F19" s="28" t="str">
+        <f aca="false">IF(N(C19)=0,"",D19/C19)</f>
+        <v/>
       </c>
       <c r="H19" s="26" t="n">
         <f aca="false">IF(13&gt;cfgRDays,"",13)</f>
@@ -23846,7 +23948,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="32" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D21" s="36" t="n">
         <f aca="false">SUMIFS(txAmt,txType,"Expense",txDate,"&gt;="&amp;cfgRStart,txDate,"&lt;="&amp;cfgREnd)</f>
@@ -23879,9 +23981,9 @@
       <c r="L22" s="7"/>
       <c r="M22" s="12"/>
     </row>
-    <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="37" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C23" s="37"/>
       <c r="H23" s="26" t="n">
@@ -23899,7 +24001,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="38" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C24" s="12" t="n">
         <v>12000</v>
@@ -23919,7 +24021,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="38" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C25" s="12" t="n">
         <v>5000</v>
@@ -23939,7 +24041,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="38" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C26" s="12" t="n">
         <v>4000</v>
@@ -23959,7 +24061,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="38" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C27" s="12" t="n">
         <v>800</v>
@@ -23979,7 +24081,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="38" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C28" s="12" t="n">
         <v>1500</v>
@@ -23999,7 +24101,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="32" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C29" s="36" t="n">
         <f aca="false">C24+C25+C26+C27-C28</f>
@@ -24020,7 +24122,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="32" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C30" s="36" t="n">
         <f aca="false">cfgNisab</f>
@@ -24041,7 +24143,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="32" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C31" s="39" t="str">
         <f aca="false">IF(C29&gt;=C30,"Yes","No")</f>
@@ -24062,7 +24164,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="32" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C32" s="22" t="n">
         <f aca="false">IF(C29&gt;=C30,C29*0.025,0)</f>
@@ -24097,7 +24199,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="40" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C34" s="40"/>
       <c r="D34" s="40"/>
@@ -24156,19 +24258,19 @@
       <c r="I37" s="41"/>
       <c r="J37" s="21" t="str">
         <f aca="false">COUNTIF(J7:J36,"✓")&amp;" / "&amp;cfgRDays</f>
-        <v>0 / 30</v>
+        <v>12 / 30</v>
       </c>
       <c r="K37" s="42" t="n">
         <f aca="false">SUM(K7:K36)</f>
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="L37" s="21" t="str">
         <f aca="false">COUNTIF(L7:L36,"✓")&amp;" / "&amp;cfgRDays</f>
-        <v>0 / 30</v>
+        <v>10 / 30</v>
       </c>
       <c r="M37" s="22" t="n">
         <f aca="false">SUM(M7:M36)</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -24186,7 +24288,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5A2927F1-7F1B-4620-81A3-19963C35D4C0}</x14:id>
+          <x14:id>{A180443D-CE71-434A-BF55-48A1C4BDE5FA}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24212,7 +24314,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5A2927F1-7F1B-4620-81A3-19963C35D4C0}">
+          <x14:cfRule type="dataBar" id="{A180443D-CE71-434A-BF55-48A1C4BDE5FA}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
